--- a/backend/data/orders.xlsx
+++ b/backend/data/orders.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:V5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,6 +433,39 @@
       <c r="K1" t="str">
         <v>created_at</v>
       </c>
+      <c r="L1" t="str">
+        <v>quote_status</v>
+      </c>
+      <c r="M1" t="str">
+        <v>quote_version</v>
+      </c>
+      <c r="N1" t="str">
+        <v>customer_notes</v>
+      </c>
+      <c r="O1" t="str">
+        <v>admin_notes</v>
+      </c>
+      <c r="P1" t="str">
+        <v>negotiation_count</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>quote_sent_at</v>
+      </c>
+      <c r="R1" t="str">
+        <v>quote_accepted_at</v>
+      </c>
+      <c r="S1" t="str">
+        <v>is_price_hidden</v>
+      </c>
+      <c r="T1" t="str">
+        <v>delivery_charges</v>
+      </c>
+      <c r="U1" t="str">
+        <v>quote_valid_until</v>
+      </c>
+      <c r="V1" t="str">
+        <v>previous_quote_id</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -468,6 +501,33 @@
       <c r="K2" t="str">
         <v>2026-03-13T09:46:39.311Z</v>
       </c>
+      <c r="L2" t="str">
+        <v>FINALIZED</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>2026-03-13T09:46:39.311Z</v>
+      </c>
+      <c r="R2" t="str">
+        <v>2026-03-13T09:46:39.311Z</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -503,6 +563,33 @@
       <c r="K3" t="str">
         <v>2026-03-13T09:46:46.615Z</v>
       </c>
+      <c r="L3" t="str">
+        <v>FINALIZED</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>2026-03-13T09:46:46.615Z</v>
+      </c>
+      <c r="R3" t="str">
+        <v>2026-03-13T09:46:46.615Z</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -538,6 +625,33 @@
       <c r="K4" t="str">
         <v>2026-03-13T09:54:18.596Z</v>
       </c>
+      <c r="L4" t="str">
+        <v>FINALIZED</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>2026-03-13T09:54:18.596Z</v>
+      </c>
+      <c r="R4" t="str">
+        <v>2026-03-13T09:54:18.596Z</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -573,10 +687,37 @@
       <c r="K5" t="str">
         <v>2026-03-13T09:54:32.564Z</v>
       </c>
+      <c r="L5" t="str">
+        <v>FINALIZED</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>2026-03-13T09:54:32.564Z</v>
+      </c>
+      <c r="R5" t="str">
+        <v>2026-03-13T09:54:32.564Z</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V5"/>
   </ignoredErrors>
 </worksheet>
 </file>